--- a/Collections/EURO/Lithuania/#EURO#Lithuania#Regular#[2015-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Lithuania/#EURO#Lithuania#Regular#[2015-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Lithuania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BE8059-B4AE-47F9-BCE3-7F726E4CE821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DF881F-D331-4BBC-9932-5115CAC0CC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -388,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="55">
   <si>
     <t>-</t>
   </si>
@@ -528,12 +531,6 @@
     <t>7.000</t>
   </si>
   <si>
-    <t>2.000.000</t>
-  </si>
-  <si>
-    <t>8.000.000</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
@@ -544,6 +541,21 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>8.007.000</t>
+  </si>
+  <si>
+    <t>2.007.000</t>
+  </si>
+  <si>
+    <t>3.007.000</t>
+  </si>
+  <si>
+    <t>3.006.000</t>
+  </si>
+  <si>
+    <t>9.007.000</t>
   </si>
 </sst>
 </file>
@@ -925,7 +937,111 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="51">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1246,9 +1362,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="14" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1548,13 +1664,13 @@
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33"/>
       <c r="B2" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -1759,6 +1875,50 @@
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" ref="G12:G13" si="3">IF(OR(AND(F12&gt;1,F12&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -1795,12 +1955,12 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="containsText" dxfId="37" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1812,11 +1972,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F11">
+    <cfRule type="containsText" dxfId="48" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1828,12 +2005,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
-    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
+  <conditionalFormatting sqref="F12:F13">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1884,13 +2061,13 @@
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33"/>
       <c r="B2" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -2052,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" ref="G9:G11" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G9:G13" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2100,7 +2277,49 @@
         <v/>
       </c>
     </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="P13" s="29"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2123,11 +2342,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5">
-    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F5">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="46" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2139,12 +2375,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="45" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2156,12 +2392,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
+  <conditionalFormatting sqref="F8:F11">
+    <cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2173,12 +2409,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
-    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
+  <conditionalFormatting sqref="F12:F13">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2198,7 +2434,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="3" customWidth="1"/>
@@ -2229,13 +2465,13 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33"/>
       <c r="B2" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -2393,7 +2629,7 @@
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F9" s="18">
         <v>0</v>
@@ -2415,13 +2651,13 @@
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F10" s="18">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="str">
-        <f t="shared" ref="G10:G11" si="2">IF(OR(AND(F10&gt;1,F10&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G10:G13" si="2">IF(OR(AND(F10&gt;1,F10&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2437,12 +2673,56 @@
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F11" s="18">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -2454,11 +2734,62 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F5">
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F5">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="42" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="41" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2470,12 +2801,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="29" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
+  <conditionalFormatting sqref="F9:F11">
+    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:F11">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2487,29 +2818,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2521,12 +2835,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F11">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F11">
+  <conditionalFormatting sqref="F13">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2577,13 +2891,13 @@
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -2757,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" ref="G9:G11" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G9:G13" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2812,9 +3126,53 @@
       <c r="R11" s="29"/>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="R12" s="29"/>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="R13" s="29"/>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2828,11 +3186,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5">
-    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F5">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="37" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2844,12 +3219,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="24" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="36" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2861,12 +3236,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="23" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
+  <conditionalFormatting sqref="F8 F10">
+    <cfRule type="containsText" dxfId="35" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10 F8">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2878,12 +3253,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8 F10">
-    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8 F10">
+  <conditionalFormatting sqref="F9">
+    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2895,12 +3270,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
+  <conditionalFormatting sqref="F11">
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2912,12 +3287,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
+  <conditionalFormatting sqref="F12:F13">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2968,13 +3343,13 @@
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -3148,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" ref="G9:G11" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G9:G13" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3196,6 +3571,54 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3223,11 +3646,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5">
-    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F5">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3239,12 +3679,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3256,12 +3696,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
+  <conditionalFormatting sqref="F8:F11">
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3273,12 +3713,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
+  <conditionalFormatting sqref="F12:F13">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3329,13 +3769,13 @@
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -3509,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" ref="G9:G11" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G9:G13" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3561,7 +4001,53 @@
         <v/>
       </c>
     </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="T13" s="29"/>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3584,11 +4070,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F5">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3600,12 +4103,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="26" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3617,12 +4120,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
+  <conditionalFormatting sqref="F8:F11">
+    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3634,12 +4137,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
+  <conditionalFormatting sqref="F12:F13">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3690,13 +4193,13 @@
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -3870,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" ref="G9:G11" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G9:G13" si="1">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3918,6 +4421,54 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3945,11 +4496,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F5">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="23" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3961,12 +4529,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3978,12 +4546,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
+  <conditionalFormatting sqref="F8:F11">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3995,12 +4563,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
+  <conditionalFormatting sqref="F12:F13">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4051,13 +4619,13 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -4231,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" ref="G9:G11" si="2">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G9:G13" si="2">IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4280,6 +4848,54 @@
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f t="shared" ref="G13" si="3">IF(OR(AND(F13&gt;1,F13&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4321,11 +4937,79 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7 F9">
+    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7 F9">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="containsText" dxfId="17" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4337,46 +5021,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7 F9">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9 F7">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4388,12 +5038,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
+  <conditionalFormatting sqref="F13">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
